--- a/backtest_runs/20260410_193731/by_symbol/FANM/FANM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FANM/FANM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-2995.019999999995</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>104159.75</v>
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>108319.5</v>
@@ -817,7 +817,7 @@
         <v>-4492.529999999992</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>104991.7</v>
@@ -955,7 +955,7 @@
         <v>-6489.209999999995</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>99168.05</v>
@@ -1185,7 +1185,7 @@
         <v>-15973.44</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>108485.89</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>108485.89</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>108485.89</v>
@@ -1323,7 +1323,7 @@
         <v>-1996.680000000002</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="3" t="n">
         <v>106489.21</v>
@@ -1415,7 +1415,7 @@
         <v>-2828.629999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>105490.87</v>
@@ -1461,7 +1461,7 @@
         <v>-4825.31</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>100665.56</v>
@@ -1507,7 +1507,7 @@
         <v>-2495.850000000006</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="3" t="n">
         <v>98169.71000000001</v>
@@ -1645,7 +1645,7 @@
         <v>-166.3899999999965</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>98003.32000000001</v>
